--- a/results/Int Task Remove ACC -0.3/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002049100383031778</v>
+        <v>0.002892317574372122</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001089166602476703</v>
+        <v>0.003198807881360147</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.888349589871844e-05</v>
+        <v>0.002466082553023882</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001030877894278293</v>
+        <v>0.0005914518033496995</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008611151632008241</v>
+        <v>0.002102610290458863</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003452850029105716</v>
+        <v>-0.0002027555389910781</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002315657600939314</v>
+        <v>-2.115539185016391e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.001759680469934183</v>
+        <v>0.0002964145702008913</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01397095335175909</v>
+        <v>0.01780786123506579</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01577500823020746</v>
+        <v>0.0200553664556229</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002461709758723729</v>
+        <v>-0.0002616700164913723</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0009071448702101614</v>
+        <v>-0.0006337424217920951</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002605677140052598</v>
+        <v>0.0009132185971408201</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007455361351585076</v>
+        <v>0.01087456543532158</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009113629890764648</v>
+        <v>0.01191878386517631</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0004997340462547827</v>
+        <v>0.001136298623746123</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002170472400657379</v>
+        <v>0.0009115486407550142</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.002975859480674652</v>
+        <v>-0.002802654377646475</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004652221517684239</v>
+        <v>0.001307750933295464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001396577638622243</v>
+        <v>-5.629264657038725e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007160007221611689</v>
+        <v>0.008574661039645199</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002000424059168535</v>
+        <v>-0.002037047992593932</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001655103989988044</v>
+        <v>0.0009508059207402875</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001517732828804521</v>
+        <v>0.0003173979447106324</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001721192519487887</v>
+        <v>0.000903496795471955</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0003795444075858501</v>
+        <v>7.756144889314202e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.001952414952661634</v>
+        <v>0.003678867628738323</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.000748938095694438</v>
+        <v>-0.001846910230083102</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.001381237313916425</v>
+        <v>-0.0003230134621303159</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0007099078832349794</v>
+        <v>0.0005799236638471864</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0001115492343819147</v>
+        <v>-0.0002426856081274187</v>
       </c>
       <c r="AH3" t="n">
-        <v>-7.779333636424575e-05</v>
+        <v>1.458648741414439e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.001161915028610189</v>
+        <v>0.0001243221587372389</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.0005961371463302821</v>
+        <v>-0.001090954543495586</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0004323365507425336</v>
+        <v>-0.0004173258032567295</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002547993567385465</v>
+        <v>0.0003565338524307915</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001885648677517497</v>
+        <v>0.001407947410293523</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001948455187462066</v>
+        <v>-0.001900486816099031</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0006181725409350747</v>
+        <v>0.0004715878418497388</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001284441590946894</v>
+        <v>0.001097208899891708</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.002605816255538488</v>
+        <v>-0.00137387039730517</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.001843119591384535</v>
+        <v>-0.0009437918109508304</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0004273614276904192</v>
+        <v>-0.001306888121761241</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.00287087456759566</v>
+        <v>0.001348024527640234</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0008947738652866101</v>
+        <v>0.0006521257992761919</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.00171603850083024</v>
+        <v>-0.001973861952941503</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.195452540025844e-05</v>
+        <v>-0.0001231689080386256</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0007877062057412487</v>
+        <v>0.0002131416797110597</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.00274616147478431</v>
+        <v>-0.001564520593715583</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.004064026231623613</v>
+        <v>-0.004636784737415697</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001529675835218136</v>
+        <v>-0.003872962657371632</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0001767190836936883</v>
+        <v>-0.0002711520872051033</v>
       </c>
       <c r="BD3" t="n">
-        <v>-5.867530384779906e-06</v>
+        <v>-0.0003673107044940927</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0003507548425808294</v>
+        <v>-0.0001097025979719369</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0004491392380320956</v>
+        <v>-0.0030555595906152</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002562786312049676</v>
+        <v>-0.00385271900299749</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.993115833582749e-06</v>
+        <v>-2.993115833582749e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0002736477152928751</v>
+        <v>-0.0002537126261460176</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.0006593193912460329</v>
+        <v>-0.0003661219506800205</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0008676274719940436</v>
+        <v>-0.00278809438737455</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0004211206112715537</v>
+        <v>-0.0001775391721717856</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.000818120521060731</v>
+        <v>-0.001248469917214218</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.003045243708387243</v>
+        <v>-0.001716453006339637</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0001599985246983625</v>
+        <v>0.0001836876713601974</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.001294974386422273</v>
+        <v>0.001704277274244342</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0003362473486463702</v>
+        <v>0.0001909685032916264</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.002867694503482588</v>
+        <v>0.001382210968239596</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.765859798719452e-05</v>
+        <v>-0.0007955130526567332</v>
       </c>
       <c r="BT3" t="n">
-        <v>2.112078310990802e-05</v>
+        <v>0.0005698221497850764</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.00206477223178731</v>
+        <v>0.003306977146576287</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001480674717110748</v>
+        <v>0.0005727357075341543</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.001910345058163103</v>
+        <v>-0.002747405247285216</v>
       </c>
       <c r="BX3" t="n">
-        <v>-7.580083288192817e-05</v>
+        <v>-7.80026119456434e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>-5.841847207695319e-05</v>
+        <v>0.000196869600435382</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0002523187963649887</v>
+        <v>-3.449232438546338e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.238616298289808e-05</v>
+        <v>5.988023952094856e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>7.376384533615778e-05</v>
+        <v>-7.01869063260807e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0001993470377771556</v>
+        <v>0.0002104785615025829</v>
       </c>
       <c r="CD3" t="n">
-        <v>-5.610908498674406e-06</v>
+        <v>-7.482993197279187e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-2.753489707798096e-05</v>
+        <v>0.0001376568042223414</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0006184371645169051</v>
+        <v>0.000176385814399127</v>
       </c>
       <c r="CG3" t="n">
-        <v>-5.239739997410908e-05</v>
+        <v>-0.0005026665395863949</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0004817947067789284</v>
+        <v>-0.0004845057701608291</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0007577675679412389</v>
+        <v>0.0005074236857262537</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.002515587220891084</v>
+        <v>0.003457423185206701</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.001246530117685981</v>
+        <v>-0.00186160798526469</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003037933616260942</v>
+        <v>0.004557033704336153</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01118812697695982</v>
+        <v>0.01036762408215054</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003070453462348816</v>
+        <v>0.00458339013023338</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00409272030599394</v>
+        <v>0.003211793890124087</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004820164575302263</v>
+        <v>0.005060259617530058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006343678276859274</v>
+        <v>0.008742460455834704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003931847371340468</v>
+        <v>0.0003286731575150641</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005030013701364266</v>
+        <v>0.004789552824237812</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01852149749816678</v>
+        <v>0.01304414815528664</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02226209549664868</v>
+        <v>0.01553829610388376</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00496502858549108</v>
+        <v>0.005552019142868416</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003125147558633606</v>
+        <v>0.007054518895676952</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004840430635156438</v>
+        <v>0.00692748184763427</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01480092076580053</v>
+        <v>0.01715443435908119</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009265150691343885</v>
+        <v>0.008874520562832328</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004463250777559625</v>
+        <v>0.005506583355342178</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004970719156230991</v>
+        <v>0.005365596783831637</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007178603427653742</v>
+        <v>0.006850042577765347</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003358654018287044</v>
+        <v>0.005119452780045347</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003639299680814501</v>
+        <v>0.0003819949559509826</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007887261937640624</v>
+        <v>0.01156087364440565</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006073647502552445</v>
+        <v>0.004788964301204791</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004585882946303142</v>
+        <v>0.002050261904989849</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002475725653196677</v>
+        <v>0.002429011102986758</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004829375427732518</v>
+        <v>0.003995708773316458</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001795997035340526</v>
+        <v>0.0005973050715840498</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006225830104531654</v>
+        <v>0.008732021051997571</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008422217456825119</v>
+        <v>0.006869259364624997</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004816796126219052</v>
+        <v>0.00717570892189856</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00896078762077861</v>
+        <v>0.008361881097190431</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0007005337748094935</v>
+        <v>0.0005013284877188406</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0006847019191178603</v>
+        <v>0.0005789023686472438</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007305383079617063</v>
+        <v>0.008634317625246617</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.008255369435428903</v>
+        <v>0.005283701776166681</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001240286121560307</v>
+        <v>0.0009520045547313133</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0008600074967050726</v>
+        <v>0.0009342663832585388</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.006195220874636096</v>
+        <v>0.005329108072736504</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.005369090381585345</v>
+        <v>0.005607700550510642</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001073686746461708</v>
+        <v>0.0005269889884295812</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.004524085264714831</v>
+        <v>0.003903660785412431</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.006566932408461996</v>
+        <v>0.005049509860550601</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.004644480218155634</v>
+        <v>0.003313861321448107</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.005693741788951568</v>
+        <v>0.006756021172002667</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.008325392397516453</v>
+        <v>0.007843449060418393</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.006775930815498122</v>
+        <v>0.005738530265165822</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.004058208299492234</v>
+        <v>0.005517193502386226</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0006637020149371451</v>
+        <v>0.0005960919473728553</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003973606287738469</v>
+        <v>0.006102805205998379</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.008779183069874276</v>
+        <v>0.007904446886514141</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008647320447414408</v>
+        <v>0.01123649116240706</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.007089520555503299</v>
+        <v>0.01269007487129827</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0006259655353588824</v>
+        <v>0.0006847475304216199</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001377822756883763</v>
+        <v>0.001425910302353551</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001459358956538394</v>
+        <v>0.0007972019139886039</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.005937530856317692</v>
+        <v>0.01169335496762426</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.008001355982533044</v>
+        <v>0.00928361662685742</v>
       </c>
       <c r="BH4" t="n">
         <v>9.465063334834983e-06</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0008473157730356771</v>
+        <v>0.000772525484891296</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.003979899144266348</v>
+        <v>0.005862230584410856</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.006731888382278566</v>
+        <v>0.006552492771324071</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001903245102760592</v>
+        <v>0.001506279092126919</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.004991173274740223</v>
+        <v>0.004620700137348053</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.007372309803251081</v>
+        <v>0.0105982682887731</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.006648856091259493</v>
+        <v>0.006624755152315945</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002998111739078247</v>
+        <v>0.003013374293566276</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0006291556234648784</v>
+        <v>0.0004020152290230836</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.004600502657516974</v>
+        <v>0.00507237241546231</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003253204930210986</v>
+        <v>0.003456580637357248</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002322258166317597</v>
+        <v>0.001247369594064133</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.005985933403719633</v>
+        <v>0.006007010033036956</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004241662225744639</v>
+        <v>0.002335610708746506</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.007105055135935977</v>
+        <v>0.005680528387420179</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.000433177434415633</v>
+        <v>0.0002063782718032548</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001363688727991824</v>
+        <v>0.0006779200313829305</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001652626142853102</v>
+        <v>0.001085996263876531</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.050408041461798e-05</v>
+        <v>1.893579437226274e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0009006290057339546</v>
+        <v>0.0009682358735805535</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.006768928067899392</v>
+        <v>0.002595297146523902</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.480666564241468e-05</v>
+        <v>0.0002366330221894793</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00060658277858348</v>
+        <v>0.001146232805618029</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003303972869683841</v>
+        <v>0.002925238190504848</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004980302437357693</v>
+        <v>0.005032908258372296</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.00249009804862483</v>
+        <v>0.001108193533634688</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.005403340640171847</v>
+        <v>0.00221418842161313</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.008198093351809776</v>
+        <v>0.005725684503613939</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.004116625653502973</v>
+        <v>0.003327426320915445</v>
       </c>
     </row>
     <row r="5">
@@ -1690,235 +1690,235 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004071856287425124</v>
+        <v>-0.003418252176717218</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02222222222222222</v>
+        <v>-0.01712567268122824</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004202483285577796</v>
+        <v>-0.007145145786606855</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008515352959797407</v>
+        <v>-0.004613905799423268</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.006972789115646227</v>
+        <v>-0.00748299319727892</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01088952200063311</v>
+        <v>-0.01989795918367348</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0002380952380952151</v>
+        <v>-0.0006449532408900783</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01326369104146881</v>
+        <v>-0.007303193171040135</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02257336343115128</v>
+        <v>-0.005320864237342815</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.03253789100290233</v>
+        <v>-0.0118671396323767</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.003820439350525273</v>
+        <v>-0.01397959183673468</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.005792972459639123</v>
+        <v>-0.01275720164609054</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.008196721311475386</v>
+        <v>-0.008741496598639464</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.02088435374149657</v>
+        <v>-0.01969387755102041</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.003959171048561682</v>
+        <v>0.002947773149631528</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01057296612852169</v>
+        <v>-0.007502374169040838</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007574850299401181</v>
+        <v>-0.008911564625850344</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.02238095238095236</v>
+        <v>-0.01928571428571428</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.006514027732989392</v>
+        <v>-0.003775510204081634</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.000340241261985752</v>
+        <v>-0.0009029345372460918</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.00576131687242798</v>
+        <v>-0.01107945552389997</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005758829144129807</v>
+        <v>-0.0100664767331434</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.00374072879716224</v>
+        <v>-0.002585034013605425</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.001399936366528776</v>
+        <v>-0.003061224489795911</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004454067429631892</v>
+        <v>-0.005272108843537415</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.004843304843304841</v>
+        <v>-0.0008272351256760513</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.005790645879732737</v>
+        <v>-0.01259892371003484</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01161676646706585</v>
+        <v>-0.01658752769863883</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0102870041921961</v>
+        <v>-0.01341502741051277</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01497309275087052</v>
+        <v>-0.008197278911564609</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001076289965178878</v>
+        <v>-0.000986318803690689</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001156462585033957</v>
+        <v>-0.0008595988538682486</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01183918961696739</v>
+        <v>-0.01228236783792342</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0125039569484014</v>
+        <v>-0.008958531180753427</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.001766467065868238</v>
+        <v>-0.001602050624799745</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001257658819735608</v>
+        <v>-0.0008277618592805291</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005442176870748261</v>
+        <v>-0.008293763849319402</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01193415637860082</v>
+        <v>-0.01035149951628511</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0009029345372460806</v>
+        <v>-9.67429861335467e-05</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003711722858026578</v>
+        <v>-0.003503401360544201</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.0140277329893583</v>
+        <v>-0.008749602290804936</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003849825007954166</v>
+        <v>-0.008768597657486565</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.008622754491017948</v>
+        <v>-0.01591836734693877</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.01394989174141661</v>
+        <v>-0.01271265078874113</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.01165234001910217</v>
+        <v>-0.006813116841770173</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01180272108843533</v>
+        <v>-0.01180272108843538</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001209035952911208</v>
+        <v>-0.0008547008547008739</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004008908685968826</v>
+        <v>-0.01268707482993197</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.02265306122448977</v>
+        <v>-0.02282312925170068</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01863945578231287</v>
+        <v>-0.03251700680272109</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.0147959183673469</v>
+        <v>-0.03629251700680271</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0005698005698005826</v>
+        <v>-0.001424501424501456</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001677746122190593</v>
+        <v>-0.002322621699013627</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.002929003502069383</v>
+        <v>-0.001519468186134887</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01438775510204078</v>
+        <v>-0.03561224489795918</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01398203592814369</v>
+        <v>-0.02602040816326531</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-2.993115833582749e-05</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.002228589621139754</v>
+        <v>-0.001368990767271594</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.008341292581980242</v>
+        <v>-0.01411564625850339</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.009449570474069325</v>
+        <v>-0.01371301304486156</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.003672048116492532</v>
+        <v>-0.002612060625604673</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01107927411652336</v>
+        <v>-0.005884353741496606</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01636054421768705</v>
+        <v>-0.03023809523809524</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01092117758784425</v>
+        <v>-0.01353741496598639</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.003088188475007936</v>
+        <v>-0.002160593356981655</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0002394492666866199</v>
+        <v>-0.0002865329512894754</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.001846545686087186</v>
+        <v>-0.01079274116523404</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.005102040816326503</v>
+        <v>-0.007006802721088457</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.003355492244381098</v>
+        <v>-0.002484286141873682</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.009137217446672997</v>
+        <v>-0.009646609360076452</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004520853231454913</v>
+        <v>-0.004273504273504281</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.007481693728112027</v>
+        <v>-0.01155682903533909</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0008863564419120063</v>
+        <v>-0.0003165558721114348</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.001736526946107786</v>
+        <v>-0.0005767382249279085</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003374721426297322</v>
+        <v>-0.00112866817155759</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
@@ -1927,31 +1927,31 @@
         <v>-0.001167315175097272</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01209805794333012</v>
+        <v>-0.004141637685741361</v>
       </c>
       <c r="CD5" t="n">
-        <v>-5.988023952094856e-05</v>
+        <v>-0.0007482993197279186</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0007317849188673287</v>
+        <v>-0.001945525291828787</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.005986394557823083</v>
+        <v>-0.00502687322162505</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.00719516077682264</v>
+        <v>-0.01142857142857144</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.006856287425149687</v>
+        <v>-0.002395209580838331</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.008659662527857348</v>
+        <v>-0.003023046991918577</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.006267806267806287</v>
+        <v>-0.001580135440180619</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.009678446354664083</v>
+        <v>-0.006734693877551023</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001093944566132105</v>
+        <v>-0.0005136995714174697</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.003566053571798095</v>
+        <v>-0.0001028657326575255</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001354481250011191</v>
+        <v>0.0009918843509290674</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001651724164053117</v>
+        <v>-0.001199832868974143</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002753599948231275</v>
+        <v>-0.0004490842197146572</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.003836927866915107</v>
+        <v>-0.003587696291979131</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.163323782234389e-05</v>
+        <v>-3.34643879823654e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.003350223126787397</v>
+        <v>-0.002431340429196674</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003849162159295791</v>
+        <v>0.01146388334552422</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00738438025544296</v>
+        <v>0.01524851143129862</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.00028578839715033</v>
+        <v>-0.001249088703246701</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002146171229233432</v>
+        <v>-0.00393956983991201</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002574496635372653</v>
+        <v>-0.002250086395263096</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001245738865978333</v>
+        <v>0.002733080004296595</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003111865788042548</v>
+        <v>0.00485450264872109</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001450670711608978</v>
+        <v>-0.002947609066199866</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001066194915947011</v>
+        <v>-0.002759608946157685</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.002090839977315526</v>
+        <v>-0.004872020468732583</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0005797385502618435</v>
+        <v>-0.001781854055875926</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.000169694760313574</v>
+        <v>-0.0001966475212839852</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002932545904643469</v>
+        <v>0.002318146220113335</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003532559076789102</v>
+        <v>-0.005283999823363259</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.002750087214372931</v>
+        <v>-0.0004082168824615151</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0004144250823538226</v>
+        <v>-0.001534777667485196</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001661174492068512</v>
+        <v>-0.002301980992904484</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0007561861286214721</v>
+        <v>-0.000365519440011558</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0005371539134841092</v>
+        <v>0.001201436301244235</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.005986304439476037</v>
+        <v>-0.004987789909870766</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002906432600913325</v>
+        <v>-0.00501140935375558</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.003382195621655748</v>
+        <v>-0.005268251508926522</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0005387087114755885</v>
+        <v>-0.0005402172445062026</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0005325440298378558</v>
+        <v>-0.0004602586467373465</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.00529388785722284</v>
+        <v>-0.005290106862575375</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.003201059635949094</v>
+        <v>-0.005525552458557267</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0003492540223388518</v>
+        <v>-0.001050073828805281</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.001055847488696057</v>
+        <v>-0.0005292695595577407</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001732239458049881</v>
+        <v>-0.0006209744078916057</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.005635995722494897</v>
+        <v>-0.00497481518781881</v>
       </c>
       <c r="AP6" t="n">
-        <v>-3.370984871862716e-05</v>
+        <v>0.0001154505431638586</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.002335325186328036</v>
+        <v>-0.0003900437016690544</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.0066402422457646</v>
+        <v>-0.004923192941304343</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0006076210255212211</v>
+        <v>-0.001984451591191769</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.005952440803275616</v>
+        <v>-0.003386966424215729</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.001191913728241967</v>
+        <v>-0.002873238114078977</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.00170312371778277</v>
+        <v>-0.003868817995444815</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.00292926519370783</v>
+        <v>-0.003689160816883161</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.000237282741198444</v>
+        <v>-0.0004110201486597076</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0007863331579049642</v>
+        <v>-0.001539239415873422</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0061217016463708</v>
+        <v>-0.002117786277191203</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.01053169781044167</v>
+        <v>-0.00733909027118921</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0008728289059544536</v>
+        <v>-0.00686198366834789</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0004005003364807774</v>
+        <v>-0.0006446383634468034</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0008955447213268074</v>
+        <v>-0.001485102782119668</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.000296996900918367</v>
+        <v>-0.0003561490724897226</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.002038264113379637</v>
+        <v>-0.001315979241008908</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.007645345405663737</v>
+        <v>-0.007087372336912778</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0005026885438563972</v>
+        <v>-0.0008447768993155636</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.003537625381114373</v>
+        <v>-0.001487842295214814</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.007652773298935807</v>
+        <v>-0.008397363218791795</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.001236049942275586</v>
+        <v>-0.001302944580610332</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0032842414454265</v>
+        <v>-0.005181553566152522</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.006690352929004034</v>
+        <v>-0.001764009625322707</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001996203925696327</v>
+        <v>-0.002912355804151029</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0012133631725954</v>
+        <v>-0.0006411202991476989</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.546551190845236e-05</v>
+        <v>-8.115297760775964e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0002617020170376016</v>
+        <v>0.0004789478212088194</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001340127583102071</v>
+        <v>-0.002884241231901219</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0004482558283623539</v>
+        <v>0.0004455052048877389</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001535358928330943</v>
+        <v>0.001064620256642312</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001081050799763594</v>
+        <v>0.0002076706343022178</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.003788492058199844</v>
+        <v>-0.007462021604560559</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0001818390899842731</v>
+        <v>-0.0002271184788185055</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001174695761781283</v>
+        <v>-0.0002082060369057892</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0006264590078996295</v>
+        <v>-0.0008196759919786856</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0005193123781090852</v>
+        <v>-0.001004812730141627</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001577048257564209</v>
+        <v>-0.001129537363656008</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0004212312190166545</v>
+        <v>-0.000334765648189303</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002937421791009934</v>
+        <v>-0.0007670212622160112</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.003826385690158144</v>
+        <v>-0.002420931839205625</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0008835726130156456</v>
+        <v>-0.0009878229647193731</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0008099981901955655</v>
+        <v>-0.001021013548853195</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.002812412298039663</v>
+        <v>-0.001152832933332776</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.002365814788093198</v>
+        <v>-0.004294727432584594</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002600966469018468</v>
+        <v>0.002180479597024482</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00340309177563245</v>
+        <v>0.001653122326775008</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0003784137960545331</v>
+        <v>0.003303439822484844</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0005222116370271757</v>
+        <v>-4.226241394763013e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0006960863510014792</v>
+        <v>0.001296742213734392</v>
       </c>
       <c r="H7" t="n">
-        <v>6.844523877183595e-05</v>
+        <v>0.002019833277656214</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001568288092672177</v>
+        <v>7.766982506027809e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.00211728815769166</v>
+        <v>0.0008169730029096377</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01900595130439362</v>
+        <v>0.01618130875492784</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01474507033878484</v>
+        <v>0.02112471224498547</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007613529306579492</v>
+        <v>0.001287504935380429</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0004913610582874817</v>
+        <v>0.001436695600119703</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0003799913877501614</v>
+        <v>9.092547917226019e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007088538591244759</v>
+        <v>0.009254288974962464</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00560524411711814</v>
+        <v>0.009288498564047981</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0007040848813260114</v>
+        <v>0.001625339838934936</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002355041664214586</v>
+        <v>0.001413024637474064</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0006380710869145878</v>
+        <v>-0.002325177120766542</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001154688334580844</v>
+        <v>0.001111171577103204</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001249068813939214</v>
+        <v>1.53823197834968e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006453532415193275</v>
+        <v>0.009400909811265002</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.002124915305431052</v>
+        <v>-0.001666260582552054</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001639058228677959</v>
+        <v>0.000740216039940117</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001441668281768488</v>
+        <v>0.000334014946876382</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0007475533716260252</v>
+        <v>0.001724607752457064</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001764624263886849</v>
+        <v>0.0001114294810569794</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0002210874442361954</v>
+        <v>0.004491683173427453</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.001925118083015054</v>
+        <v>-0.001935544024186836</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.000826654660606857</v>
+        <v>0.001353790963113044</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.002068614547794623</v>
+        <v>-0.0007446319289681425</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0004122092975884728</v>
+        <v>-0.0002702822943934757</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0001038521112404212</v>
+        <v>0.0002049232041519467</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.002723473778326802</v>
+        <v>-0.00253170704767105</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.001862008356223432</v>
+        <v>-0.0004240445158357697</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0004821689933061868</v>
+        <v>-0.0005787450111607527</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0001275694180855324</v>
+        <v>0.0003993335483177263</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001534194268504552</v>
+        <v>0.002413861792597066</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.00060677884751264</v>
+        <v>-0.001241476237307254</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.000313295941206082</v>
+        <v>0.0004146960804440325</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0007315694556465247</v>
+        <v>0.000931692416637503</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.002014076422376532</v>
+        <v>-0.0009967757368080032</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0007671678760309887</v>
+        <v>-0.000158023120161177</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.001927657325361715</v>
+        <v>0.0007480710307613214</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.002884606472318157</v>
+        <v>0.00103083007773625</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0008465700339289283</v>
+        <v>0.001471084077259666</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0005151094221589991</v>
+        <v>-0.0002646606562004272</v>
       </c>
       <c r="AX7" t="n">
-        <v>-1.927126423995063e-07</v>
+        <v>-0.0002820664342574164</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0001830716534642118</v>
+        <v>-1.38898757638229e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.001344059571271305</v>
+        <v>0.000839870801666387</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.002251153828156776</v>
+        <v>-0.003078756527060511</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001629549942164371</v>
+        <v>1.983113702579977e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0003511054760975518</v>
+        <v>-0.0003401886582037883</v>
       </c>
       <c r="BD7" t="n">
-        <v>-8.778361644056765e-05</v>
+        <v>-0.0005419724066671183</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0001207795604233897</v>
+        <v>2.994011976046873e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0005381786570126501</v>
+        <v>0.0005251996908298639</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.003452480474643676</v>
+        <v>-0.003547917726672289</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-6.032075682110284e-05</v>
+        <v>-0.0001325225349733672</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0007900627993775167</v>
+        <v>-0.0002989607752005629</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0002849458227911327</v>
+        <v>-0.0005468394004689069</v>
       </c>
       <c r="BL7" t="n">
-        <v>-4.993938286946832e-05</v>
+        <v>-0.0001081645647753093</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0005263868594010789</v>
+        <v>-0.003268197760546643</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.003029163831978865</v>
+        <v>-0.0001577139166844432</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0005139047401227948</v>
+        <v>0.001069414628639887</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.001439648668018373</v>
+        <v>0.001220243239497476</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0001111573938603228</v>
+        <v>9.410970967824728e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001170077300685457</v>
+        <v>0.001439848829809137</v>
       </c>
       <c r="BS7" t="n">
-        <v>-6.186204763378168e-05</v>
+        <v>-0.001303462118080084</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0001586813165147582</v>
+        <v>0.0005646869526253484</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.002483915821325166</v>
+        <v>0.003441088623397304</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0009114099222121086</v>
+        <v>0.0004346889908312834</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0003602100877750369</v>
+        <v>-0.002275187727461209</v>
       </c>
       <c r="BX7" t="n">
-        <v>-9.190332916761968e-05</v>
+        <v>-0.0001277154961978111</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.000108426255905586</v>
+        <v>6.327114206414186e-05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.881391562685749e-05</v>
+        <v>-0.0003288458653370852</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-6.271909958895374e-05</v>
+        <v>6.049298556157212e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001456563297549118</v>
+        <v>0.0002463469821878727</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-6.802721088432495e-05</v>
+        <v>-3.079785348582554e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0003866377977111091</v>
+        <v>0.0007669526208255895</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.084115458101532e-07</v>
+        <v>-0.00148320906417016</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001109557036307884</v>
+        <v>-0.0004451737020982727</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.499246344187634e-05</v>
+        <v>0.001139617697895384</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0004728476780237024</v>
+        <v>0.001096438040751613</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0008263149695428018</v>
+        <v>-0.001054855783434777</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.004039939337558413</v>
+        <v>0.005930339984577071</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004699171521572739</v>
+        <v>0.005134531732707665</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001089541551962051</v>
+        <v>0.0042958001843941</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001836082658621582</v>
+        <v>0.001573273955274995</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003820338413564475</v>
+        <v>0.006155770709464462</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00473901723145459</v>
+        <v>0.005838477665561381</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004848107718777194</v>
+        <v>0.0001507494645377777</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0008417799190946124</v>
+        <v>0.00376811809569208</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0228564924028092</v>
+        <v>0.02849679189765797</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03070588315451349</v>
+        <v>0.02876391957618684</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004600543810338536</v>
+        <v>0.002956077187019557</v>
       </c>
       <c r="N8" t="n">
-        <v>4.306622426257511e-05</v>
+        <v>0.003788121205048975</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003504413583238017</v>
+        <v>0.005245527352956442</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01453657133888549</v>
+        <v>0.01753971170405852</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01811828621958364</v>
+        <v>0.01920618924770811</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00239227537258182</v>
+        <v>0.003547272122452327</v>
       </c>
       <c r="S8" t="n">
-        <v>0.004449351499743967</v>
+        <v>0.004687118562917611</v>
       </c>
       <c r="T8" t="n">
-        <v>9.69584493518144e-07</v>
+        <v>0.0009621050527826497</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001944708902658085</v>
+        <v>0.001834658032466099</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000369991903054695</v>
+        <v>0.0001263812306256856</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01173541183685199</v>
+        <v>0.01340215609433329</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001485450842824118</v>
+        <v>0.0023512415413</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004551165991995535</v>
+        <v>0.002398074501942099</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002754860585917471</v>
+        <v>0.001110136141888132</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003979345854821914</v>
+        <v>0.002990630530338428</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006318914557939842</v>
+        <v>0.000337516275830621</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.005601200134833728</v>
+        <v>0.01119846153267027</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002527361927889737</v>
+        <v>0.003221434912097307</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0008938382033915115</v>
+        <v>0.003781513391032729</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.006282290527704664</v>
+        <v>0.0008261065181396215</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0003426047231574358</v>
+        <v>0.0001199745997135682</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0001935963960253584</v>
+        <v>0.0004602494670417539</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0003173542688551384</v>
+        <v>0.004997616110297834</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.006599070513939181</v>
+        <v>0.00266763871806113</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001019802507897766</v>
+        <v>0.0001028607775706098</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002296957199232202</v>
+        <v>0.001116056096713947</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002668032697885478</v>
+        <v>0.004035338841052063</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001340117025938101</v>
+        <v>1.479639879826413e-05</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001309669166812058</v>
+        <v>0.0005313375799453956</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002385558731743176</v>
+        <v>0.00142228191550165</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.002232371990712476</v>
+        <v>0.001462091885777053</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001765808226914323</v>
+        <v>0.001100218748375717</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.004542581138687201</v>
+        <v>0.00109975148059249</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.008039806621991833</v>
+        <v>0.006051254150943633</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.003520866875047099</v>
+        <v>0.002858187190646086</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0008777672053572411</v>
+        <v>0.0013836471815412</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0003544939420463605</v>
+        <v>0.00010074725535138</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001211228248643961</v>
+        <v>0.003450094063337089</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002675501778362763</v>
+        <v>0.001680623534513676</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.003443902534906446</v>
+        <v>0.003505816563126846</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.00639569846828685</v>
+        <v>0.003685180890287986</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0004508422952265917</v>
+        <v>0.000127636586443941</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0003088898462811574</v>
+        <v>0.0007360923721218826</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0003602517406591843</v>
+        <v>0.0001279397730909099</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003676493801343226</v>
+        <v>0.002476562049820044</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.004584968619061508</v>
+        <v>0.003885604683682164</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0002692336396865086</v>
+        <v>0.0002086853972615072</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002083248676383545</v>
+        <v>0.001769204106151259</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.004750749217896613</v>
+        <v>0.002132732573835402</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0002488131932597115</v>
+        <v>0.0007986881427499537</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001289594879541142</v>
+        <v>0.003344457055447719</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001419366830861793</v>
+        <v>0.002433537128347341</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.004182930050950506</v>
+        <v>0.005234409620001886</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.003903309989979845</v>
+        <v>0.003601094596881504</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0003407643220448092</v>
+        <v>0.0003699564498313212</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.004198853116873111</v>
+        <v>0.003120896392012545</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002096585067419182</v>
+        <v>0.002215442770637469</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0002643383530919918</v>
+        <v>0.001305200216038002</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.005867551176496219</v>
+        <v>0.007917431558358598</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001801308456393744</v>
+        <v>0.001095452572316022</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.007114311723034289</v>
+        <v>0.001048741909162995</v>
       </c>
       <c r="BX8" t="n">
-        <v>-8.326672684688674e-18</v>
+        <v>-8.503401360551722e-06</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0006535372031918535</v>
+        <v>0.0001355125607261337</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0005117590923636728</v>
+        <v>0.0004005717295998773</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003279718242978402</v>
+        <v>0.0005271048161556214</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001155345211581321</v>
+        <v>0.001985762908581151</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0001825014080701487</v>
+        <v>0.0007084218963370221</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002091489641646213</v>
+        <v>0.001352388529241291</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003992987327376563</v>
+        <v>0.003853897359592038</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.000431731139630051</v>
+        <v>0.0003777979020243238</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0009391432829850472</v>
+        <v>0.00199459389651406</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.00260584584861262</v>
+        <v>0.006102950301068113</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0001571049759206522</v>
+        <v>-0.0001767362508531933</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006312079461711017</v>
+        <v>0.009832437559279183</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02044540674296322</v>
+        <v>0.01967213114754094</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007050268732216247</v>
+        <v>0.008846272811630019</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004870233899391241</v>
+        <v>0.006217135787194517</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007961688117330112</v>
+        <v>0.009218796767434867</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0106255612092188</v>
+        <v>0.008659662527857326</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000916851090736659</v>
+        <v>0.0004190362167015849</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005656988925471396</v>
+        <v>0.007672715695638299</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03804250224483685</v>
+        <v>0.03612690811134389</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04541916167664674</v>
+        <v>0.04505988023952093</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01163088753604616</v>
+        <v>0.004805564337654134</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005845963501391926</v>
+        <v>0.007206928549334945</v>
       </c>
       <c r="O9" t="n">
-        <v>0.008490868311438683</v>
+        <v>0.01416640890813481</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03200598802395212</v>
+        <v>0.03835329341317365</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02292808771364071</v>
+        <v>0.02697056030389364</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00435757769945534</v>
+        <v>0.01155342711762943</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01076289965178855</v>
+        <v>0.008979347500748247</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00211470682473569</v>
+        <v>0.005815032477574977</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005387608500448948</v>
+        <v>0.01456851221775436</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007954183900731992</v>
+        <v>0.0005064893953782956</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01919256648510097</v>
+        <v>0.03208620173600718</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01394791978449572</v>
+        <v>0.003502994011976035</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.009790419161676667</v>
+        <v>0.003711463633642609</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.005988023952095823</v>
+        <v>0.005209580838323335</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01047904191616767</v>
+        <v>0.006736526946107757</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001359468858678492</v>
+        <v>0.001287039808440582</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0147305389221557</v>
+        <v>0.01299103000309306</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01445578231292521</v>
+        <v>0.006345405567195428</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.006344120474207004</v>
+        <v>0.01089494163424121</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01288048702338998</v>
+        <v>0.01616282550134695</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001227177491768927</v>
+        <v>0.0005988023952095744</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0009877282250823072</v>
+        <v>0.0007142857142857006</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01336220228889579</v>
+        <v>0.01716671821837298</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01119047619047624</v>
+        <v>0.006345405567195428</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.002819609099647569</v>
+        <v>0.001616282550134684</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001209035952911241</v>
+        <v>0.001718103722558117</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.01589820359281439</v>
+        <v>0.00895209580838322</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003435374149659909</v>
+        <v>0.008103928240024715</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002663873091888647</v>
+        <v>0.001551123773345997</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.01074850299401199</v>
+        <v>0.01095808383233532</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.00787189464232263</v>
+        <v>0.00674296319208163</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.01149097815764483</v>
+        <v>0.003000309310238103</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.004906616017727128</v>
+        <v>0.008103928240024682</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01368953525134367</v>
+        <v>0.01460640526788388</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.01520958083832338</v>
+        <v>0.01020958083832333</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001991779955738238</v>
+        <v>0.004191616766467043</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0011972463334331</v>
+        <v>0.001190476190476164</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01105414931111827</v>
+        <v>0.01095480395091286</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.007768226679401502</v>
+        <v>0.005740083843921284</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0063154744088596</v>
+        <v>0.006062480668110093</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01002693804250224</v>
+        <v>0.005838323353293406</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001360965047943119</v>
+        <v>0.000748502994011957</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.003292427416941024</v>
+        <v>0.001763068357562592</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001902612060625552</v>
+        <v>0.001422827095576795</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.005703300224287122</v>
+        <v>0.003268183274591463</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.007145145786606888</v>
+        <v>0.004330343334364295</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.993115833582749e-05</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0006728612624159136</v>
+        <v>0.0009180120291231609</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.004710028836911273</v>
+        <v>0.009161676646706574</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.008426786286446686</v>
+        <v>0.004940119760479045</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.003043896187119532</v>
+        <v>0.002531239987183576</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.006616766467065893</v>
+        <v>0.005179640718562873</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.00885235535883654</v>
+        <v>0.00835079317569587</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.009832437559279161</v>
+        <v>0.007542651900628528</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.005222685036847185</v>
+        <v>0.006394428616650826</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001870748299319769</v>
+        <v>0.001054421768707492</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01249599487343803</v>
+        <v>0.00921768707482994</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.005799423261775105</v>
+        <v>0.004082895143829224</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.004609398383717433</v>
+        <v>0.00221082986222364</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.009557823129251741</v>
+        <v>0.01095808383233531</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01047619047619053</v>
+        <v>0.004934315924383204</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01223966677347008</v>
+        <v>0.005927587311759064</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0008982035928143839</v>
+        <v>0.0003093102381688473</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.002787568087151582</v>
+        <v>0.001484689143210594</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002040816326530648</v>
+        <v>0.001922460749759702</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.000192246074975988</v>
+        <v>5.988023952094856e-05</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002006802721088474</v>
+        <v>0.001768707482993181</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01531560397308559</v>
+        <v>0.004221556886227528</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.363347120585949e-05</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001322154143824539</v>
+        <v>0.002074829931972788</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002604010775216992</v>
+        <v>0.004037167574495348</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.007529637936558831</v>
+        <v>0.005351067120321651</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002721088435374208</v>
+        <v>0.0009183673469387643</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01316885613585391</v>
+        <v>0.003450499838761656</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01938481256007694</v>
+        <v>0.0149631528356296</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.006247997436719044</v>
+        <v>0.004082895143829213</v>
       </c>
     </row>
   </sheetData>
